--- a/docs/Group6_PRG381_Project_RequiredHardware.xlsx
+++ b/docs/Group6_PRG381_Project_RequiredHardware.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\OneDrive\Desktop\PRJ381_Project\Required Hardware\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\OneDrive\Desktop\cogniflight-edge\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C29C3FF3-4068-403B-83A4-CC928EF63FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52119BA4-C324-48BC-B47F-A1DCC9B7A9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BD184DE-096E-4408-BB28-F2172AC6A2E6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
   <si>
     <t>Category</t>
   </si>
@@ -171,6 +171,21 @@
   </si>
   <si>
     <t xml:space="preserve">Total: </t>
+  </si>
+  <si>
+    <t>Hardware Components</t>
+  </si>
+  <si>
+    <t>100 µF electrolytic capacitor (≥10 V)</t>
+  </si>
+  <si>
+    <t>0.1 µF ceramic capacitor</t>
+  </si>
+  <si>
+    <t>in parallel (right at the motor terminals) to snub high-frequency switching noise</t>
+  </si>
+  <si>
+    <t>directly across the motor leads to buffer the startup current spike.</t>
   </si>
 </sst>
 </file>
@@ -178,7 +193,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot;R&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -225,10 +240,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F512B1D-9D20-4760-9F3A-F70BEBFA0BD1}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -803,6 +818,27 @@
         <v>4185.3100000000004</v>
       </c>
     </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Group6_PRG381_Project_RequiredHardware.xlsx
+++ b/docs/Group6_PRG381_Project_RequiredHardware.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\OneDrive\Desktop\cogniflight-edge\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52119BA4-C324-48BC-B47F-A1DCC9B7A9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7F2B9C-BF6F-4DC5-BBE2-BDD76FAE4D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BD184DE-096E-4408-BB28-F2172AC6A2E6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
   <si>
     <t>Category</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Prevent thermal throttling under load</t>
   </si>
   <si>
-    <t>HKD FANDC005030-07 (for Pi 4)</t>
-  </si>
-  <si>
     <t>Networking</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>Facial recognition, eye-blink &amp; yawning detection, night vision</t>
   </si>
   <si>
-    <t>Raspberry Pi Camera Module 3W</t>
-  </si>
-  <si>
     <t>Storage &amp; Power</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t>Wireless Heart Rate Monitor</t>
   </si>
   <si>
-    <t>Heart rate &amp; variability (ANT+ &amp; Bluetooth)</t>
-  </si>
-  <si>
     <t>Magene H64 Chest Strap Monitor</t>
   </si>
   <si>
@@ -140,9 +131,6 @@
     <t>Seat vibration</t>
   </si>
   <si>
-    <t>HKD Flat DC Vibrator Motor (3 V)</t>
-  </si>
-  <si>
     <t>Audible Alert</t>
   </si>
   <si>
@@ -155,12 +143,6 @@
     <t>Visual Indicators</t>
   </si>
   <si>
-    <t>Status LEDs (green, yellow, red, blue) + resistors</t>
-  </si>
-  <si>
-    <t>Standard LEDs + 330 Ω resistors</t>
-  </si>
-  <si>
     <t>Source</t>
   </si>
   <si>
@@ -170,29 +152,81 @@
     <t>Takealot</t>
   </si>
   <si>
-    <t xml:space="preserve">Total: </t>
-  </si>
-  <si>
-    <t>Hardware Components</t>
-  </si>
-  <si>
-    <t>100 µF electrolytic capacitor (≥10 V)</t>
-  </si>
-  <si>
-    <t>0.1 µF ceramic capacitor</t>
-  </si>
-  <si>
-    <t>in parallel (right at the motor terminals) to snub high-frequency switching noise</t>
-  </si>
-  <si>
-    <t>directly across the motor leads to buffer the startup current spike.</t>
+    <t>Environmental Sensors</t>
+  </si>
+  <si>
+    <t>Temperature and Humidity sensor</t>
+  </si>
+  <si>
+    <t>Temperature &amp; Humidity in Cockpit</t>
+  </si>
+  <si>
+    <t>Pilot heart rate &amp; variability (ANT+ &amp; Bluetooth)</t>
+  </si>
+  <si>
+    <t>HKD TEMP+HUMD DHT22 SENSOR</t>
+  </si>
+  <si>
+    <t>BMT M20 VIBRATOR MOTOR 1.5-6V</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Resistors</t>
+  </si>
+  <si>
+    <t>LED current-limiting &amp; sensor pull-ups</t>
+  </si>
+  <si>
+    <t>Transistors</t>
+  </si>
+  <si>
+    <t>Capacitors</t>
+  </si>
+  <si>
+    <t>Power-rail decoupling &amp; bulk filtering</t>
+  </si>
+  <si>
+    <t>GPIO-driven switching for motor</t>
+  </si>
+  <si>
+    <t>PN2222A/2N2222A</t>
+  </si>
+  <si>
+    <t>Standard LEDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status LEDs (green, yellow, red, blue) </t>
+  </si>
+  <si>
+    <t>Assorted kit: 3*220Ω + 1kΩ + 4.7kΩ</t>
+  </si>
+  <si>
+    <t>Assorted kit: 0.1 µF ceramic (X7R0104K52T),10 µF electrolytic (&gt;=10V)</t>
+  </si>
+  <si>
+    <t>Heatsink Kit</t>
+  </si>
+  <si>
+    <t>Raspberry Pi 4 Heatsink Set (3-pack)</t>
+  </si>
+  <si>
+    <t>Passive cooling for CPU</t>
+  </si>
+  <si>
+    <t>HKD FANDC005030-07</t>
+  </si>
+  <si>
+    <t>RASPBERRY PI CAM MODULE 3W NOIR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;R&quot;#,##0;[Red]\-&quot;R&quot;#,##0"/>
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
@@ -232,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -244,6 +278,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F512B1D-9D20-4760-9F3A-F70BEBFA0BD1}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -606,7 +641,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -626,7 +661,7 @@
         <v>2003.3</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -640,13 +675,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3">
         <v>45</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -654,189 +689,262 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3">
-        <v>835</v>
+        <v>816.5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E6" s="3">
         <v>75</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E7" s="3">
         <v>161</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E8" s="3">
         <v>990</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3">
         <v>10.01</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="3">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="3">
+      <c r="D12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="4">
+        <v>79.010000000000005</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D12" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="4">
+        <v>12.28</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="4">
-        <f>SUM(E2:E11)</f>
-        <v>4185.3100000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
         <v>49</v>
       </c>
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="5">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>47</v>
+      <c r="A16" t="s">
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="5">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="4">
+        <f>SUM(E2:E16)</f>
+        <v>4261.1000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Group6_PRG381_Project_RequiredHardware.xlsx
+++ b/docs/Group6_PRG381_Project_RequiredHardware.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\OneDrive\Desktop\cogniflight-edge\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7F2B9C-BF6F-4DC5-BBE2-BDD76FAE4D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3ADEAC-5B9C-491B-B575-01142CDDA98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7BD184DE-096E-4408-BB28-F2172AC6A2E6}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>Execute ML inference (TensorFlow Lite), run OpenCV pipelines</t>
   </si>
   <si>
-    <t>Raspberry Pi 4 Model B (8 GB RAM)</t>
-  </si>
-  <si>
     <t>Cooling Fan</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>Camera Module</t>
   </si>
   <si>
-    <t>Facial recognition, eye-blink &amp; yawning detection, night vision</t>
-  </si>
-  <si>
     <t>Storage &amp; Power</t>
   </si>
   <si>
@@ -107,12 +101,6 @@
     <t>Power Supply</t>
   </si>
   <si>
-    <t>Stable 5 V power for Pi 4 and peripherals</t>
-  </si>
-  <si>
-    <t>SMPS 5 V, 3 A (compatible with Raspberry Pi 4)</t>
-  </si>
-  <si>
     <t>Biosensors</t>
   </si>
   <si>
@@ -206,19 +194,31 @@
     <t>Assorted kit: 0.1 µF ceramic (X7R0104K52T),10 µF electrolytic (&gt;=10V)</t>
   </si>
   <si>
-    <t>Heatsink Kit</t>
-  </si>
-  <si>
-    <t>Raspberry Pi 4 Heatsink Set (3-pack)</t>
-  </si>
-  <si>
-    <t>Passive cooling for CPU</t>
-  </si>
-  <si>
-    <t>HKD FANDC005030-07</t>
-  </si>
-  <si>
     <t>RASPBERRY PI CAM MODULE 3W NOIR</t>
+  </si>
+  <si>
+    <t>5B camera cable</t>
+  </si>
+  <si>
+    <t>RASPBERRY PI 5B 16GB</t>
+  </si>
+  <si>
+    <t>RASPBERRY PI 5B active cooler</t>
+  </si>
+  <si>
+    <t>RASPBERRY PI 5B PSU 5V 5A TYPE-C</t>
+  </si>
+  <si>
+    <t>Stable 5 V power for Pi 5 and peripherals</t>
+  </si>
+  <si>
+    <t>camera cable</t>
+  </si>
+  <si>
+    <t>camera adapter cable</t>
+  </si>
+  <si>
+    <t>Facial recognition, eye-blink &amp; yawning detection</t>
   </si>
 </sst>
 </file>
@@ -641,7 +641,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -655,13 +655,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E2" s="3">
-        <v>2003.3</v>
+        <v>3180</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -669,19 +669,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -689,193 +689,193 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3">
         <v>816.5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="E6" s="3">
         <v>75</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E7" s="3">
-        <v>161</v>
+        <v>299</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3">
         <v>990</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3">
         <v>21</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3">
         <v>10.01</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3">
         <v>12</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="E12" s="4">
         <v>79.010000000000005</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5">
         <v>20</v>
@@ -883,42 +883,42 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E14" s="4">
         <v>12.28</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E15" s="5">
         <v>3</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -926,25 +926,25 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E16" s="5">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E17" s="4">
         <f>SUM(E2:E16)</f>
-        <v>4261.1000000000004</v>
+        <v>5662.8</v>
       </c>
     </row>
   </sheetData>
